--- a/customer_satisfaction_evaluation_forms/031_drive_thru_service_satisfaction_poll--customer_satisfaction_evaluation_forms.xlsx
+++ b/customer_satisfaction_evaluation_forms/031_drive_thru_service_satisfaction_poll--customer_satisfaction_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -757,8 +757,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -786,12 +786,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_fast'}</t>
+          <t>very_fast</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very fast'}</t>
+          <t>Very fast</t>
         </is>
       </c>
     </row>
@@ -803,12 +803,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'fast'}</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Fast'}</t>
+          <t>Fast</t>
         </is>
       </c>
     </row>
@@ -820,12 +820,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -837,12 +837,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'slow'}</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Slow'}</t>
+          <t>Slow</t>
         </is>
       </c>
     </row>
@@ -854,12 +854,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'very_slow'}</t>
+          <t>very_slow</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Very slow'}</t>
+          <t>Very slow</t>
         </is>
       </c>
     </row>
@@ -871,12 +871,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'very_accurate'}</t>
+          <t>very_accurate</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Very accurate'}</t>
+          <t>Very accurate</t>
         </is>
       </c>
     </row>
@@ -888,12 +888,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'mostly_accurate'}</t>
+          <t>mostly_accurate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Mostly accurate'}</t>
+          <t>Mostly accurate</t>
         </is>
       </c>
     </row>
@@ -905,12 +905,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_accurate'}</t>
+          <t>somewhat_accurate</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat accurate'}</t>
+          <t>Somewhat accurate</t>
         </is>
       </c>
     </row>
@@ -922,12 +922,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_accurate'}</t>
+          <t>not_very_accurate</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Not very accurate'}</t>
+          <t>Not very accurate</t>
         </is>
       </c>
     </row>
@@ -939,12 +939,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_accurate'}</t>
+          <t>not_at_all_accurate</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all accurate'}</t>
+          <t>Not at all accurate</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Very good'}</t>
+          <t>Very good</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -990,12 +990,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'average'}</t>
+          <t>average</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Average'}</t>
+          <t>Average</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1024,12 +1024,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'very_clean'}</t>
+          <t>very_clean</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Very clean'}</t>
+          <t>Very clean</t>
         </is>
       </c>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'mostly_clean'}</t>
+          <t>mostly_clean</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Mostly clean'}</t>
+          <t>Mostly clean</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_clean'}</t>
+          <t>somewhat_clean</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat clean'}</t>
+          <t>Somewhat clean</t>
         </is>
       </c>
     </row>
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'not_very_clean'}</t>
+          <t>not_very_clean</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Not very clean'}</t>
+          <t>Not very clean</t>
         </is>
       </c>
     </row>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_clean'}</t>
+          <t>not_at_all_clean</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all clean'}</t>
+          <t>Not at all clean</t>
         </is>
       </c>
     </row>
@@ -1126,12 +1126,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'dissatisfied'}</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Dissatisfied'}</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
